--- a/artfynd/S 7097-2022 artfynd.xlsx
+++ b/artfynd/S 7097-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479728</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479729</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479730</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479731</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479732</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479978</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479979</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479984</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479988</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479989</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479997</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/916635</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678614</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678615</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678616</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678617</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678618</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3003,6 +3108,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678619</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,6 +3224,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678621</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3225,6 +3340,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678623</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3336,6 +3456,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678624</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3447,6 +3572,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678626</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3558,6 +3688,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678627</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3669,6 +3804,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678631</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3776,6 +3916,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7131124</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3878,6 +4023,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7131121</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3980,6 +4130,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7131125</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4082,6 +4237,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7131126</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4184,8 +4344,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7131123</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>